--- a/esyluban/examples/dev/DataTables/test/list.xlsx
+++ b/esyluban/examples/dev/DataTables/test/list.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbNotIndexList" &amp; value_type="test.NotIndexList" &amp; mode="list" &amp; read_schema_from_file="false" &amp; input="not_index@test/list.xlsx" &amp; output="test_tbnotindexlist"</t>
+          <t>full_name="test.TbNotIndexList" &amp; mode="list"</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
@@ -539,7 +539,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbMultiIndexList" &amp; value_type="test.MultiIndexList" &amp; index="id1,id2,id3" &amp; mode="list" &amp; read_schema_from_file="false" &amp; input="multi_index@test/list.xlsx" &amp; output="test_tbmultiindexlist"</t>
+          <t>full_name="test.TbMultiIndexList" &amp; index="id1,id2,id3" &amp; mode="list"</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -842,7 +836,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbMultiUnionIndexList" &amp; value_type="test.MultiUnionIndexList" &amp; index="id1+id2+id3" &amp; mode="list" &amp; read_schema_from_file="false" &amp; input="multi_union_index@test/list.xlsx" &amp; output="test_tbmultiunionindexlist"</t>
+          <t>full_name="test.TbMultiUnionIndexList" &amp; index="id1+id2+id3" &amp; mode="list"</t>
         </is>
       </c>
     </row>
